--- a/data/trans_orig/P16A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43490</t>
+          <t>44612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70220</t>
+          <t>72076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107611</t>
+          <t>108029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99860</t>
+          <t>99330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143821</t>
+          <t>141150</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>988233</t>
+          <t>987111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1011299</t>
+          <t>1011028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1207502</t>
+          <t>1207084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1244893</t>
+          <t>1243037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2203014</t>
+          <t>2205685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2246975</t>
+          <t>2247505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34540</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57330</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91925</t>
+          <t>91534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78562</t>
+          <t>80125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117231</t>
+          <t>118337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1657854</t>
+          <t>1656364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1676825</t>
+          <t>1677315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1495748</t>
+          <t>1496139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1530343</t>
+          <t>1530378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3162836</t>
+          <t>3161730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3201505</t>
+          <t>3199942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30576</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27065</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25334</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520832</t>
+          <t>522486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540185</t>
+          <t>540656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449347</t>
+          <t>450157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>466018</t>
+          <t>467036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>979273</t>
+          <t>979458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1002486</t>
+          <t>1004403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58615</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94985</t>
+          <t>91669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>154672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204663</t>
+          <t>206254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220429</t>
+          <t>222735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281987</t>
+          <t>286084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3180540</t>
+          <t>3183856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3216910</t>
+          <t>3218135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3174534</t>
+          <t>3172943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3225050</t>
+          <t>3224525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6372735</t>
+          <t>6368638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6434293</t>
+          <t>6431987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28827</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88066</t>
+          <t>88595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129555</t>
+          <t>130431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105048</t>
+          <t>106415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148916</t>
+          <t>148763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>943010</t>
+          <t>944376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>963224</t>
+          <t>963368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1203036</t>
+          <t>1202160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1244525</t>
+          <t>1243996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2155512</t>
+          <t>2155665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2199380</t>
+          <t>2198013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32058</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60019</t>
+          <t>60370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97077</t>
+          <t>95575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80412</t>
+          <t>79346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120979</t>
+          <t>120073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1927964</t>
+          <t>1927306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1947338</t>
+          <t>1946560</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1652693</t>
+          <t>1654195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1689751</t>
+          <t>1689400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3588813</t>
+          <t>3589719</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3629380</t>
+          <t>3630446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17602</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,82 +3037,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>26584</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17404</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>37067</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>34371</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>22878</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>26584</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>16788</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>38654</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>34371</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>22734</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>48726</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462730</t>
+          <t>463692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477323</t>
+          <t>477565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,82 +3150,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>431070</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>420587</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>440250</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>903615</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>891315</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>915108</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>96,34%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>431070</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>419000</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>440866</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>903615</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>889260</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>915252</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>61974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183913</t>
+          <t>185191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>242673</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225138</t>
+          <t>224630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>291876</t>
+          <t>291014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3349224</t>
+          <t>3350217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3380174</t>
+          <t>3379971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3300103</t>
+          <t>3297342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3356102</t>
+          <t>3354824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6660330</t>
+          <t>6661192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6727068</t>
+          <t>6727576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70081</t>
+          <t>69957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51052</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>83236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>734865</t>
+          <t>734408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>747544</t>
+          <t>747842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>924579</t>
+          <t>924703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>955297</t>
+          <t>954604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1666008</t>
+          <t>1665771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1697955</t>
+          <t>1699839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>35053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>51102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84555</t>
+          <t>82458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>73553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110940</t>
+          <t>112586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2040933</t>
+          <t>2041332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2061149</t>
+          <t>2060940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1903745</t>
+          <t>1905842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1936428</t>
+          <t>1937198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3953745</t>
+          <t>3952099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3993791</t>
+          <t>3991132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>37523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534026</t>
+          <t>534094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544732</t>
+          <t>544661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512078</t>
+          <t>511617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531641</t>
+          <t>531798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1050633</t>
+          <t>1051392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073410</t>
+          <t>1073867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>31466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>57091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124896</t>
+          <t>123773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173078</t>
+          <t>172110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163180</t>
+          <t>161569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218496</t>
+          <t>215108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3320363</t>
+          <t>3320527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3346168</t>
+          <t>3346152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3359022</t>
+          <t>3359990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3407204</t>
+          <t>3408327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6691222</t>
+          <t>6694610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6746538</t>
+          <t>6748149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>31779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50815</t>
+          <t>51608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74947</t>
+          <t>74012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70456</t>
+          <t>71465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98299</t>
+          <t>100206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481506</t>
+          <t>481673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498068</t>
+          <t>498277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>676785</t>
+          <t>677720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>700917</t>
+          <t>700124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1166884</t>
+          <t>1164977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1194727</t>
+          <t>1193718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>61113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>105231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>93418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142713</t>
+          <t>142952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2242452</t>
+          <t>2242497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2267849</t>
+          <t>2267823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2130138</t>
+          <t>2131914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2175689</t>
+          <t>2176032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4384759</t>
+          <t>4384520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4433947</t>
+          <t>4434054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>22838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32576</t>
+          <t>32814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>57518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626269</t>
+          <t>625553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640447</t>
+          <t>640384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617066</t>
+          <t>617410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>636948</t>
+          <t>637625</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249001</t>
+          <t>1249568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1274510</t>
+          <t>1274272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50955</t>
+          <t>50859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>85680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147543</t>
+          <t>146893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202463</t>
+          <t>208149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214440</t>
+          <t>212256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>283157</t>
+          <t>280387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3362793</t>
+          <t>3364722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3399447</t>
+          <t>3399543</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3446876</t>
+          <t>3441190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3501796</t>
+          <t>3502446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6816585</t>
+          <t>6819355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6885302</t>
+          <t>6887486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44612</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72076</t>
+          <t>73536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108029</t>
+          <t>108201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99330</t>
+          <t>97784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141150</t>
+          <t>141671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>987111</t>
+          <t>987904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1011028</t>
+          <t>1011939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1207084</t>
+          <t>1206912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1243037</t>
+          <t>1241577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2205685</t>
+          <t>2205164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2247505</t>
+          <t>2249051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57295</t>
+          <t>57983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91534</t>
+          <t>89655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80125</t>
+          <t>79202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118337</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1656364</t>
+          <t>1657770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1677315</t>
+          <t>1676839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1496139</t>
+          <t>1498018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1530378</t>
+          <t>1529690</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3161730</t>
+          <t>3160091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3199942</t>
+          <t>3200865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23417</t>
+          <t>25055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>49083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522486</t>
+          <t>521446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540656</t>
+          <t>540347</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450157</t>
+          <t>449710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>467036</t>
+          <t>465905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>979458</t>
+          <t>978737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1004403</t>
+          <t>1002765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57390</t>
+          <t>56909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91669</t>
+          <t>93723</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>152853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206254</t>
+          <t>207030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222735</t>
+          <t>224272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286084</t>
+          <t>290756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3183856</t>
+          <t>3181802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3218135</t>
+          <t>3218616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3172943</t>
+          <t>3172167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3224525</t>
+          <t>3226344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6368638</t>
+          <t>6363966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6431987</t>
+          <t>6430450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88595</t>
+          <t>88569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130431</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106415</t>
+          <t>103664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148763</t>
+          <t>146628</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>944376</t>
+          <t>941708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>963368</t>
+          <t>962284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1202160</t>
+          <t>1200900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1243996</t>
+          <t>1244022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2155665</t>
+          <t>2157800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2198013</t>
+          <t>2200764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60370</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95575</t>
+          <t>97976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79346</t>
+          <t>78804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120073</t>
+          <t>119358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1927306</t>
+          <t>1926731</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1946560</t>
+          <t>1947286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1654195</t>
+          <t>1651794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1689400</t>
+          <t>1688701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3589719</t>
+          <t>3590434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3630446</t>
+          <t>3630988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46671</t>
+          <t>48723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463692</t>
+          <t>462608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477565</t>
+          <t>477425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420587</t>
+          <t>419099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440250</t>
+          <t>440336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891315</t>
+          <t>889263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>915108</t>
+          <t>913765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61974</t>
+          <t>61503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185191</t>
+          <t>182794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>242673</t>
+          <t>244535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224630</t>
+          <t>229351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>291014</t>
+          <t>293620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3350217</t>
+          <t>3350688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3379971</t>
+          <t>3380343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3297342</t>
+          <t>3295480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3354824</t>
+          <t>3357221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6661192</t>
+          <t>6658586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6727576</t>
+          <t>6722855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40056</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>69369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49168</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83236</t>
+          <t>86684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>734408</t>
+          <t>734542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>747842</t>
+          <t>748150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>924703</t>
+          <t>925291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>954604</t>
+          <t>955887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1665771</t>
+          <t>1662323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1699839</t>
+          <t>1698083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>35274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>52777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82458</t>
+          <t>85480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73553</t>
+          <t>72445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112586</t>
+          <t>110231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2041332</t>
+          <t>2041111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2060940</t>
+          <t>2061452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1905842</t>
+          <t>1902820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1937198</t>
+          <t>1935523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3952099</t>
+          <t>3954454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3991132</t>
+          <t>3992240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17342</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37523</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>45348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534094</t>
+          <t>532926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544661</t>
+          <t>544608</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511617</t>
+          <t>511910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531798</t>
+          <t>532058</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1051392</t>
+          <t>1050679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073867</t>
+          <t>1074233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31466</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57091</t>
+          <t>57794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123773</t>
+          <t>124807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172110</t>
+          <t>171575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161569</t>
+          <t>161701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215108</t>
+          <t>213706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3320527</t>
+          <t>3319824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3346152</t>
+          <t>3347449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3359990</t>
+          <t>3360525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3408327</t>
+          <t>3407293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6694610</t>
+          <t>6696012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6748149</t>
+          <t>6748017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62511</t>
+          <t>65462</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51608</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74012</t>
+          <t>79401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>84848</t>
+          <t>88170</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71465</t>
+          <t>74205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100206</t>
+          <t>104612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>491115</t>
+          <t>554339</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481673</t>
+          <t>545329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498277</t>
+          <t>562352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>689221</t>
+          <t>754323</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>677720</t>
+          <t>740384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>700124</t>
+          <t>764216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1180335</t>
+          <t>1308662</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1164977</t>
+          <t>1292220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1193718</t>
+          <t>1322627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>56773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,67 +5915,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>96679</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61113</t>
+          <t>81562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105231</t>
+          <t>115018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>137993</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>120048</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>161436</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>119510</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>93418</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>142952</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2256022</t>
+          <t>2189252</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2242497</t>
+          <t>2173793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2267823</t>
+          <t>2201890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,67 +6028,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2151940</t>
+          <t>2074028</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2131914</t>
+          <t>2055689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2176032</t>
+          <t>2089145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4263281</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4239838</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4281226</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>97,27%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4715</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4407962</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4384520</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4434054</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43053</t>
+          <t>47774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>48143</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57518</t>
+          <t>61663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>634551</t>
+          <t>699426</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625553</t>
+          <t>690461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640384</t>
+          <t>705303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>628868</t>
+          <t>698895</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617410</t>
+          <t>687103</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637625</t>
+          <t>707369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1263419</t>
+          <t>1398321</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249568</t>
+          <t>1384801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1274272</t>
+          <t>1410001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68715</t>
+          <t>76183</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50859</t>
+          <t>61675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85680</t>
+          <t>96733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>179311</t>
+          <t>198124</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146893</t>
+          <t>175594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208149</t>
+          <t>222999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>248026</t>
+          <t>274307</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212256</t>
+          <t>247095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280387</t>
+          <t>304685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3381687</t>
+          <t>3443017</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3364722</t>
+          <t>3422467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3399543</t>
+          <t>3457525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3470028</t>
+          <t>3527245</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3441190</t>
+          <t>3502370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3502446</t>
+          <t>3549775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6851716</t>
+          <t>6970263</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6819355</t>
+          <t>6939885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6887486</t>
+          <t>6997475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
